--- a/TemplateAC_PO_YINSON - ATLANTA.xlsx
+++ b/TemplateAC_PO_YINSON - ATLANTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://odsmetering-my.sharepoint.com/personal/m_bandeira_odsenergysolutions_com/Documents/Documents/AC's_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_791F7CF95C8EFBDFC39378EDCAECABA28E3BA773" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BDBABC7-BC40-4A48-9C11-01D5BE7F8A5E}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_791F7CF95C8EFBDFC39378EDCAECABA28E3BA773" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F8A364-F5D1-4D3B-8B05-28ED9422590F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15480" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template Formulário" sheetId="1" r:id="rId1"/>
@@ -630,31 +630,104 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -662,79 +735,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -765,7 +765,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>609889</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>221838</xdr:rowOff>
+      <xdr:rowOff>218663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -813,9 +813,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>844838</xdr:colOff>
+      <xdr:colOff>848013</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>218367</xdr:rowOff>
+      <xdr:rowOff>221542</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1146,80 +1146,80 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="41" t="s">
+    <row r="1" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="22"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
+    </row>
+    <row r="6" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="25"/>
-    </row>
-    <row r="7" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="33"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1229,80 +1229,80 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:8" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="17" t="s">
+      <c r="D8" s="46"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="35" t="s">
+      <c r="G8" s="46"/>
+      <c r="H8" s="35"/>
+    </row>
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="31"/>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="28" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="37"/>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="38"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="D10" s="47"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="39"/>
+    </row>
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="50" t="s">
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="56" t="s">
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="57"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
+      <c r="H12" s="30"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="53" t="s">
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="37" t="s">
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="38"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13" s="49"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1312,26 +1312,26 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="9" t="s">
         <v>13</v>
       </c>
@@ -1342,14 +1342,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+    <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="25"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="11" t="s">
         <v>17</v>
       </c>
@@ -1360,14 +1360,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+    <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="25"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="5" t="s">
         <v>17</v>
       </c>
@@ -1378,14 +1378,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+    <row r="19" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="5" t="s">
         <v>17</v>
       </c>
@@ -1396,14 +1396,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+    <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="5" t="s">
         <v>17</v>
       </c>
@@ -1414,14 +1414,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+    <row r="21" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
@@ -1432,14 +1432,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+    <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="25"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="5" t="s">
         <v>17</v>
       </c>
@@ -1450,14 +1450,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+    <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="25"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="5" t="s">
         <v>17</v>
       </c>
@@ -1468,14 +1468,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+    <row r="24" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="25"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="5" t="s">
         <v>17</v>
       </c>
@@ -1486,32 +1486,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+    <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="6" t="s">
-        <v>18</v>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="H25" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="25"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="5" t="s">
         <v>17</v>
       </c>
@@ -1522,14 +1522,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
+    <row r="27" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="25"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="5" t="s">
         <v>17</v>
       </c>
@@ -1540,14 +1540,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+    <row r="28" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="25"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="5" t="s">
         <v>17</v>
       </c>
@@ -1558,14 +1558,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+    <row r="29" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="33"/>
       <c r="F29" s="5" t="s">
         <v>17</v>
       </c>
@@ -1576,14 +1576,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+    <row r="30" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="33"/>
       <c r="F30" s="5" t="s">
         <v>17</v>
       </c>
@@ -1594,14 +1594,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="33"/>
       <c r="F31" s="5" t="s">
         <v>17</v>
       </c>
@@ -1612,14 +1612,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="33"/>
       <c r="F32" s="5" t="s">
         <v>17</v>
       </c>
@@ -1630,14 +1630,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
+    <row r="33" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="33"/>
       <c r="F33" s="5" t="s">
         <v>17</v>
       </c>
@@ -1648,14 +1648,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="27" t="s">
+    <row r="34" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="33"/>
       <c r="F34" s="5" t="s">
         <v>17</v>
       </c>
@@ -1666,140 +1666,140 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27" t="s">
+    <row r="35" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="6" t="s">
-        <v>18</v>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
+      <c r="H35" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="6" t="s">
-        <v>18</v>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
+      <c r="H36" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="6" t="s">
-        <v>18</v>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="H37" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="6" t="s">
-        <v>18</v>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27" t="s">
+      <c r="H38" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="6" t="s">
-        <v>18</v>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H39" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+      <c r="H39" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="6" t="s">
-        <v>18</v>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
+    <row r="42" spans="1:15" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-    </row>
-    <row r="43" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="32" t="s">
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+    </row>
+    <row r="43" spans="1:15" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="25"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="33"/>
       <c r="F43" s="9" t="s">
         <v>13</v>
       </c>
@@ -1810,14 +1810,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="27" t="s">
+    <row r="44" spans="1:15" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="25"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="33"/>
       <c r="F44" s="11" t="s">
         <v>17</v>
       </c>
@@ -1828,14 +1828,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27" t="s">
+    <row r="45" spans="1:15" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="25"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="33"/>
       <c r="F45" s="5" t="s">
         <v>17</v>
       </c>
@@ -1846,14 +1846,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="27" t="s">
+    <row r="46" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="25"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="33"/>
       <c r="F46" s="5" t="s">
         <v>17</v>
       </c>
@@ -1864,50 +1864,50 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="O47" s="4"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -1917,131 +1917,90 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="33" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="19"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="20"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="22"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="42"/>
+      <c r="C52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="45"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="35"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="38"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="39"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="7"/>
       <c r="D56" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="B57" s="42"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="42"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="42"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="C1:H3"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F8:H10"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A57:H59"/>
     <mergeCell ref="A53:H54"/>
@@ -2058,6 +2017,47 @@
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F8:H10"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="C1:H3"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <pageMargins left="0.8" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup scale="63" orientation="portrait" r:id="rId1"/>
